--- a/database/event/3389/event_3389_evp_summary.xlsx
+++ b/database/event/3389/event_3389_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8366</v>
+        <v>6.0712</v>
       </c>
       <c r="C2" t="n">
-        <v>2.8029</v>
+        <v>2.9156</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9365</v>
+        <v>1.9749</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8366</v>
+        <v>6.0712</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4305</v>
+        <v>2.6652</v>
       </c>
       <c r="G2" t="n">
         <v>3.4061</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4305</v>
+        <v>2.6652</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4305</v>
+        <v>2.6652</v>
       </c>
       <c r="J2" t="n">
         <v>3.4061</v>
@@ -529,7 +529,7 @@
         <v>184</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8366</v>
+        <v>6.0713</v>
       </c>
       <c r="N2" t="n">
         <v>293</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7276</v>
+        <v>5.9384</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7506</v>
+        <v>2.8518</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8925</v>
+        <v>1.9219</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7276</v>
+        <v>5.9384</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6113</v>
+        <v>2.8221</v>
       </c>
       <c r="G3" t="n">
         <v>3.1163</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6113</v>
+        <v>2.8221</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6234</v>
+        <v>2.8459</v>
       </c>
       <c r="J3" t="n">
         <v>3.1163</v>
@@ -575,7 +575,7 @@
         <v>171</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7397</v>
+        <v>5.962199999999999</v>
       </c>
       <c r="N3" t="n">
         <v>349</v>
@@ -584,173 +584,173 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5908</v>
+        <v>5.7875</v>
       </c>
       <c r="C4" t="n">
-        <v>2.6849</v>
+        <v>2.7793</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8372</v>
+        <v>1.8618</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5908</v>
+        <v>5.7875</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1802</v>
+        <v>1.1426</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4106</v>
+        <v>4.6449</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1802</v>
+        <v>1.1426</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1903</v>
+        <v>1.1426</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4106</v>
+        <v>4.6449</v>
       </c>
       <c r="K4" t="n">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="L4" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6009</v>
+        <v>5.7875</v>
       </c>
       <c r="N4" t="n">
-        <v>349</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.287</v>
+        <v>5.5827</v>
       </c>
       <c r="C5" t="n">
-        <v>2.539</v>
+        <v>2.681</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7145</v>
+        <v>1.7802</v>
       </c>
       <c r="E5" t="n">
-        <v>5.287</v>
+        <v>5.5827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6421</v>
+        <v>2.1721</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6449</v>
+        <v>3.4106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6421</v>
+        <v>2.1721</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6421</v>
+        <v>2.1903</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6449</v>
+        <v>3.4106</v>
       </c>
       <c r="K5" t="n">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="L5" t="n">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="M5" t="n">
-        <v>5.287</v>
+        <v>5.6009</v>
       </c>
       <c r="N5" t="n">
-        <v>293</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6602</v>
+        <v>5.2242</v>
       </c>
       <c r="C6" t="n">
-        <v>2.238</v>
+        <v>2.5088</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4613</v>
+        <v>1.6374</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6602</v>
+        <v>5.2242</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4182</v>
+        <v>3.1284</v>
       </c>
       <c r="G6" t="n">
-        <v>2.242</v>
+        <v>2.0958</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4182</v>
+        <v>3.1284</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4182</v>
+        <v>3.1548</v>
       </c>
       <c r="J6" t="n">
-        <v>2.242</v>
+        <v>2.0958</v>
       </c>
       <c r="K6" t="n">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6602</v>
+        <v>5.2506</v>
       </c>
       <c r="N6" t="n">
-        <v>206</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6016</v>
+        <v>5.1603</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2098</v>
+        <v>2.4781</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4376</v>
+        <v>1.612</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6016</v>
+        <v>5.1603</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5168</v>
+        <v>2.9183</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0847</v>
+        <v>2.242</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5168</v>
+        <v>2.9183</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5168</v>
+        <v>2.9183</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0847</v>
+        <v>2.242</v>
       </c>
       <c r="K7" t="n">
         <v>106</v>
@@ -759,7 +759,7 @@
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6015</v>
+        <v>5.160299999999999</v>
       </c>
       <c r="N7" t="n">
         <v>206</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5597</v>
+        <v>4.8288</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1897</v>
+        <v>2.3189</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4207</v>
+        <v>1.4799</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5597</v>
+        <v>4.8288</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4639</v>
+        <v>2.744</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0958</v>
+        <v>2.0847</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4639</v>
+        <v>2.744</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4754</v>
+        <v>2.744</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0958</v>
+        <v>2.0847</v>
       </c>
       <c r="K8" t="n">
-        <v>178</v>
+        <v>106</v>
       </c>
       <c r="L8" t="n">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5712</v>
+        <v>4.8287</v>
       </c>
       <c r="N8" t="n">
-        <v>349</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1413</v>
+        <v>4.7524</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9888</v>
+        <v>2.2823</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2516</v>
+        <v>1.4494</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1413</v>
+        <v>4.7524</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4954</v>
+        <v>2.1065</v>
       </c>
       <c r="G9" t="n">
         <v>2.6459</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4954</v>
+        <v>2.1065</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4954</v>
+        <v>2.1065</v>
       </c>
       <c r="J9" t="n">
         <v>2.6459</v>
@@ -851,7 +851,7 @@
         <v>145</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1413</v>
+        <v>4.7524</v>
       </c>
       <c r="N9" t="n">
         <v>265</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5257</v>
+        <v>3.5674</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6932</v>
+        <v>1.7132</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0029</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5257</v>
+        <v>3.5674</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1192</v>
+        <v>-0.0775</v>
       </c>
       <c r="G10" t="n">
         <v>3.6449</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1192</v>
+        <v>-0.0775</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1192</v>
+        <v>-0.0775</v>
       </c>
       <c r="J10" t="n">
         <v>3.6449</v>
@@ -897,7 +897,7 @@
         <v>184</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5257</v>
+        <v>3.5674</v>
       </c>
       <c r="N10" t="n">
         <v>293</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5</v>
+        <v>3.5617</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6808</v>
+        <v>1.7104</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9926</v>
+        <v>0.9751</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>3.5617</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8993</v>
+        <v>3.0071</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3993</v>
+        <v>0.5546</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8993</v>
+        <v>3.0071</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9175</v>
+        <v>3.0324</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3993</v>
+        <v>0.5546</v>
       </c>
       <c r="K11" t="n">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L11" t="n">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5182</v>
+        <v>3.587</v>
       </c>
       <c r="N11" t="n">
-        <v>240</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0183</v>
+        <v>3.4855</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4495</v>
+        <v>1.6738</v>
       </c>
       <c r="D12" t="n">
-        <v>0.798</v>
+        <v>0.9447</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0183</v>
+        <v>3.4855</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4637</v>
+        <v>3.8848</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5546</v>
+        <v>-0.3993</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4637</v>
+        <v>3.8848</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4752</v>
+        <v>3.9175</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5546</v>
+        <v>-0.3993</v>
       </c>
       <c r="K12" t="n">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="L12" t="n">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0298</v>
+        <v>3.5182</v>
       </c>
       <c r="N12" t="n">
-        <v>349</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9563</v>
+        <v>3.1151</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4197</v>
+        <v>1.496</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7729</v>
+        <v>0.7971</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9563</v>
+        <v>3.1151</v>
       </c>
       <c r="F13" t="n">
-        <v>2.284</v>
+        <v>1.4693</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6723</v>
+        <v>1.6458</v>
       </c>
       <c r="H13" t="n">
-        <v>2.284</v>
+        <v>1.4693</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284</v>
+        <v>1.4693</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6723</v>
+        <v>1.6458</v>
       </c>
       <c r="K13" t="n">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L13" t="n">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9563</v>
+        <v>3.1151</v>
       </c>
       <c r="N13" t="n">
-        <v>265</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9409</v>
+        <v>3.0567</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4123</v>
+        <v>1.4679</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7667</v>
+        <v>0.7739</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9409</v>
+        <v>3.0567</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2778</v>
+        <v>3.2609</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6631</v>
+        <v>-0.2042</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2778</v>
+        <v>3.2609</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2778</v>
+        <v>3.2609</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6631</v>
+        <v>-0.2042</v>
       </c>
       <c r="K14" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L14" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9409</v>
+        <v>3.0567</v>
       </c>
       <c r="N14" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8472</v>
+        <v>3.0011</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3673</v>
+        <v>1.4412</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7288</v>
+        <v>0.7517</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8472</v>
+        <v>3.0011</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4289</v>
+        <v>2.5828</v>
       </c>
       <c r="G15" t="n">
         <v>0.4183</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4289</v>
+        <v>2.5828</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4402</v>
+        <v>2.6045</v>
       </c>
       <c r="J15" t="n">
         <v>0.4183</v>
@@ -1127,7 +1127,7 @@
         <v>171</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8585</v>
+        <v>3.0228</v>
       </c>
       <c r="N15" t="n">
         <v>349</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.781</v>
+        <v>2.9563</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3355</v>
+        <v>1.4197</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7020999999999999</v>
+        <v>0.7339</v>
       </c>
       <c r="E16" t="n">
-        <v>2.781</v>
+        <v>2.9563</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3481</v>
+        <v>2.284</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4329</v>
+        <v>0.6723</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3481</v>
+        <v>2.284</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3481</v>
+        <v>2.284</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4329</v>
+        <v>0.6723</v>
       </c>
       <c r="K16" t="n">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="L16" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="M16" t="n">
-        <v>2.781</v>
+        <v>2.9563</v>
       </c>
       <c r="N16" t="n">
-        <v>148</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4026</v>
+        <v>2.9409</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1538</v>
+        <v>1.4123</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5492</v>
+        <v>0.7277</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4026</v>
+        <v>2.9409</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6068</v>
+        <v>2.2778</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2042</v>
+        <v>0.6631</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6068</v>
+        <v>2.2778</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6068</v>
+        <v>2.2778</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2042</v>
+        <v>0.6631</v>
       </c>
       <c r="K17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4026</v>
+        <v>2.9409</v>
       </c>
       <c r="N17" t="n">
-        <v>125</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3009</v>
+        <v>2.781</v>
       </c>
       <c r="C18" t="n">
-        <v>1.105</v>
+        <v>1.3355</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5082</v>
+        <v>0.664</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3009</v>
+        <v>2.781</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6551</v>
+        <v>2.3481</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6458</v>
+        <v>0.4329</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6551</v>
+        <v>2.3481</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6551</v>
+        <v>2.3481</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6458</v>
+        <v>0.4329</v>
       </c>
       <c r="K18" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="L18" t="n">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3009</v>
+        <v>2.781</v>
       </c>
       <c r="N18" t="n">
-        <v>293</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
@@ -1284,7 +1284,7 @@
         <v>1.0791</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4864</v>
+        <v>0.4513</v>
       </c>
       <c r="E19" t="n">
         <v>2.2471</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.9546</v>
+        <v>1.9441</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9387</v>
+        <v>0.9336</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3683</v>
+        <v>0.3306</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9546</v>
+        <v>1.9441</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8062</v>
+        <v>2.7957</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8516</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8062</v>
+        <v>2.7957</v>
       </c>
       <c r="I20" t="n">
         <v>2.8192</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9204</v>
+        <v>1.91</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9222</v>
+        <v>0.9172</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3544</v>
+        <v>0.317</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9204</v>
+        <v>1.91</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7862</v>
+        <v>2.7758</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8658</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7862</v>
+        <v>2.7758</v>
       </c>
       <c r="I21" t="n">
         <v>2.7992</v>
@@ -1422,7 +1422,7 @@
         <v>0.8248</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2725</v>
+        <v>0.2403</v>
       </c>
       <c r="E22" t="n">
         <v>1.7175</v>
@@ -1468,7 +1468,7 @@
         <v>0.8153</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2645</v>
+        <v>0.2325</v>
       </c>
       <c r="E23" t="n">
         <v>1.6977</v>
@@ -1514,7 +1514,7 @@
         <v>0.7857</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2396</v>
+        <v>0.2079</v>
       </c>
       <c r="E24" t="n">
         <v>1.6361</v>
@@ -1550,492 +1550,492 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3605</v>
+        <v>1.5863</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6534</v>
+        <v>0.7618</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1282</v>
+        <v>0.1881</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3605</v>
+        <v>1.5863</v>
       </c>
       <c r="F25" t="n">
-        <v>0.729</v>
+        <v>1.5863</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6315</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.729</v>
+        <v>1.5863</v>
       </c>
       <c r="I25" t="n">
-        <v>0.729</v>
+        <v>1.5863</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6315</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="L25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3605</v>
+        <v>1.5863</v>
       </c>
       <c r="N25" t="n">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3378</v>
+        <v>1.3605</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6425</v>
+        <v>0.6534</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1191</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3378</v>
+        <v>1.3605</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0676</v>
+        <v>0.729</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2702</v>
+        <v>0.6315</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0676</v>
+        <v>0.729</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0676</v>
+        <v>0.729</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2702</v>
+        <v>0.6315</v>
       </c>
       <c r="K26" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3378</v>
+        <v>1.3605</v>
       </c>
       <c r="N26" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2534</v>
+        <v>1.3378</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6019</v>
+        <v>0.6425</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0891</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2534</v>
+        <v>1.3378</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2534</v>
+        <v>1.0676</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.2702</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2534</v>
+        <v>1.0676</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2534</v>
+        <v>1.0676</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2702</v>
       </c>
       <c r="K27" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2534</v>
+        <v>1.3378</v>
       </c>
       <c r="N27" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="C28" t="n">
-        <v>0.57</v>
+        <v>0.6019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0582</v>
+        <v>0.0554</v>
       </c>
       <c r="E28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="F28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="I28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.187</v>
+        <v>1.2534</v>
       </c>
       <c r="N28" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.0735</v>
+        <v>1.187</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5155</v>
+        <v>0.57</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0123</v>
+        <v>0.029</v>
       </c>
       <c r="E29" t="n">
-        <v>1.0735</v>
+        <v>1.187</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6437</v>
+        <v>1.187</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4298</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6437</v>
+        <v>1.187</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6437</v>
+        <v>1.187</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4298</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="N29" t="n">
         <v>145</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.0735</v>
-      </c>
-      <c r="N29" t="n">
-        <v>265</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.0188</v>
+        <v>1.0735</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4893</v>
+        <v>0.5155</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0098</v>
+        <v>-0.0162</v>
       </c>
       <c r="E30" t="n">
-        <v>1.0188</v>
+        <v>1.0735</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0188</v>
+        <v>0.6437</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.4298</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0188</v>
+        <v>0.6437</v>
       </c>
       <c r="I30" t="n">
-        <v>1.0188</v>
+        <v>0.6437</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.4298</v>
       </c>
       <c r="K30" t="n">
+        <v>120</v>
+      </c>
+      <c r="L30" t="n">
         <v>145</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
-        <v>1.0188</v>
+        <v>1.0735</v>
       </c>
       <c r="N30" t="n">
-        <v>145</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9136</v>
+        <v>1.0188</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4387</v>
+        <v>0.4893</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0523</v>
+        <v>-0.038</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9136</v>
+        <v>1.0188</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9581</v>
+        <v>1.0188</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0445</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9581</v>
+        <v>1.0188</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9581</v>
+        <v>1.0188</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.0445</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9136</v>
+        <v>1.0188</v>
       </c>
       <c r="N31" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9061</v>
+        <v>0.9136</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4351</v>
+        <v>0.4387</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0553</v>
+        <v>-0.0799</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9061</v>
+        <v>0.9136</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9061</v>
+        <v>0.9581</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.0445</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9061</v>
+        <v>0.9581</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9061</v>
+        <v>0.9581</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.0445</v>
       </c>
       <c r="K32" t="n">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9061</v>
+        <v>0.9136</v>
       </c>
       <c r="N32" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4317</v>
+        <v>0.4351</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0582</v>
+        <v>-0.0829</v>
       </c>
       <c r="E33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="F33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="I33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.899</v>
+        <v>0.9061</v>
       </c>
       <c r="N33" t="n">
-        <v>190</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.749</v>
+        <v>0.899</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3597</v>
+        <v>0.4317</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1188</v>
+        <v>-0.0857</v>
       </c>
       <c r="E34" t="n">
-        <v>0.749</v>
+        <v>0.899</v>
       </c>
       <c r="F34" t="n">
-        <v>1.749</v>
+        <v>0.899</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.749</v>
+        <v>0.899</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7572</v>
+        <v>0.899</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7572000000000001</v>
+        <v>0.899</v>
       </c>
       <c r="N34" t="n">
-        <v>217</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3296</v>
+        <v>0.4069</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.1441</v>
+        <v>-0.1064</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6864</v>
+        <v>0.8472</v>
       </c>
       <c r="N35" t="n">
         <v>121</v>
@@ -2056,124 +2056,124 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4481</v>
+        <v>0.7559</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2152</v>
+        <v>0.363</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2403</v>
+        <v>-0.1428</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4481</v>
+        <v>0.7559</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4481</v>
+        <v>1.7559</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4481</v>
+        <v>1.7559</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4481</v>
+        <v>1.7707</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K36" t="n">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M36" t="n">
-        <v>0.4481</v>
+        <v>0.7706999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4479</v>
+        <v>0.5627</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2151</v>
+        <v>0.2702</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2404</v>
+        <v>-0.2197</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4479</v>
+        <v>0.5627</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2478</v>
+        <v>-0.1655</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2001</v>
+        <v>0.7282</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2478</v>
+        <v>-0.1655</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2478</v>
+        <v>-0.1655</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2001</v>
+        <v>0.7282</v>
       </c>
       <c r="K37" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="L37" t="n">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="M37" t="n">
-        <v>0.4479</v>
+        <v>0.5627</v>
       </c>
       <c r="N37" t="n">
-        <v>125</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2023</v>
+        <v>0.2346</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2512</v>
+        <v>-0.2493</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4212</v>
+        <v>0.4886</v>
       </c>
       <c r="N38" t="n">
         <v>100</v>
@@ -2194,415 +2194,415 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4076</v>
+        <v>0.4481</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1957</v>
+        <v>0.2152</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2567</v>
+        <v>-0.2654</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4076</v>
+        <v>0.4481</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.3206</v>
+        <v>0.4481</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7282</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.3206</v>
+        <v>0.4481</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3206</v>
+        <v>0.4481</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7282</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L39" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.4076</v>
+        <v>0.4481</v>
       </c>
       <c r="N39" t="n">
-        <v>265</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4049</v>
+        <v>0.4479</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1944</v>
+        <v>0.2151</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2578</v>
+        <v>-0.2655</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4049</v>
+        <v>0.4479</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4049</v>
+        <v>0.2478</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>0.2001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.4049</v>
+        <v>0.2478</v>
       </c>
       <c r="I40" t="n">
-        <v>1.4114</v>
+        <v>0.2478</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>0.2001</v>
       </c>
       <c r="K40" t="n">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M40" t="n">
-        <v>0.4114</v>
+        <v>0.4479</v>
       </c>
       <c r="N40" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3714</v>
+        <v>0.4212</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1784</v>
+        <v>0.2023</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2713</v>
+        <v>-0.2761</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3714</v>
+        <v>0.4212</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0529</v>
+        <v>0.4212</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3185</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0529</v>
+        <v>0.4212</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0529</v>
+        <v>0.4212</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3185</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.3714</v>
+        <v>0.4212</v>
       </c>
       <c r="N41" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3538</v>
+        <v>0.3996</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1699</v>
+        <v>0.1919</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2784</v>
+        <v>-0.2847</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3538</v>
+        <v>0.3996</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3538</v>
+        <v>1.3996</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3538</v>
+        <v>1.3996</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3538</v>
+        <v>1.4114</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3538</v>
+        <v>0.4114</v>
       </c>
       <c r="N42" t="n">
-        <v>100</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3306</v>
+        <v>0.3714</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1588</v>
+        <v>0.1784</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2878</v>
+        <v>-0.2959</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3306</v>
+        <v>0.3714</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3306</v>
+        <v>0.0529</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.3185</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3306</v>
+        <v>0.0529</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3306</v>
+        <v>0.0529</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.3185</v>
       </c>
       <c r="K43" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3306</v>
+        <v>0.3714</v>
       </c>
       <c r="N43" t="n">
-        <v>121</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1561</v>
+        <v>0.1683</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.29</v>
+        <v>-0.3043</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3251</v>
+        <v>0.3505</v>
       </c>
       <c r="N44" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1459</v>
+        <v>0.1561</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2986</v>
+        <v>-0.3144</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3038</v>
+        <v>0.3251</v>
       </c>
       <c r="N45" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2888</v>
+        <v>0.3038</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1387</v>
+        <v>0.1459</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3047</v>
+        <v>-0.3229</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2888</v>
+        <v>0.3038</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0144</v>
+        <v>0.3038</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.7256</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0144</v>
+        <v>0.3038</v>
       </c>
       <c r="I46" t="n">
-        <v>1.0144</v>
+        <v>0.3038</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7256</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="L46" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2887999999999999</v>
+        <v>0.3038</v>
       </c>
       <c r="N46" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2472</v>
+        <v>0.2888</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1187</v>
+        <v>0.1387</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3215</v>
+        <v>-0.3289</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2472</v>
+        <v>0.2888</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2472</v>
+        <v>1.0144</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.7256</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2472</v>
+        <v>1.0144</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2472</v>
+        <v>1.0144</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.7256</v>
       </c>
       <c r="K47" t="n">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2472</v>
+        <v>0.2887999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>190</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48">
@@ -2618,7 +2618,7 @@
         <v>0.0977</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3392</v>
+        <v>-0.3628</v>
       </c>
       <c r="E48" t="n">
         <v>0.2035</v>
@@ -2664,7 +2664,7 @@
         <v>0.0567</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3737</v>
+        <v>-0.3969</v>
       </c>
       <c r="E49" t="n">
         <v>0.1181</v>
@@ -2710,7 +2710,7 @@
         <v>0.0296</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3965</v>
+        <v>-0.4194</v>
       </c>
       <c r="E50" t="n">
         <v>0.0616</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0065</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4269</v>
+        <v>-0.4493</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0136</v>
@@ -2792,231 +2792,231 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0116</v>
+        <v>-0.0115</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4311</v>
+        <v>-0.4534</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0242</v>
+        <v>-0.0239</v>
       </c>
       <c r="N52" t="n">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0261</v>
+        <v>-0.0116</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4433</v>
+        <v>-0.4536</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0543</v>
+        <v>-0.0242</v>
       </c>
       <c r="N53" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0287</v>
+        <v>-0.0261</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4455</v>
+        <v>-0.4655</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0597</v>
+        <v>-0.0543</v>
       </c>
       <c r="N54" t="n">
-        <v>190</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0424</v>
+        <v>-0.0287</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.457</v>
+        <v>-0.4677</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.0883</v>
+        <v>-0.0597</v>
       </c>
       <c r="N55" t="n">
-        <v>68</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1114</v>
+        <v>-0.0424</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.515</v>
+        <v>-0.4791</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2319</v>
+        <v>-0.0883</v>
       </c>
       <c r="N56" t="n">
-        <v>121</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57">
@@ -3032,7 +3032,7 @@
         <v>-0.1427</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5414</v>
+        <v>-0.5623</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2971</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1542</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5511</v>
+        <v>-0.5718</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3211</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4044</v>
+        <v>-0.4066</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1942</v>
+        <v>-0.1953</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5847</v>
+        <v>-0.6059</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4044</v>
+        <v>-0.4066</v>
       </c>
       <c r="F59" t="n">
-        <v>0.5956</v>
+        <v>0.5934</v>
       </c>
       <c r="G59" t="n">
         <v>-1</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5956</v>
+        <v>0.5934</v>
       </c>
       <c r="I59" t="n">
         <v>0.5984</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4419</v>
+        <v>-0.444</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2122</v>
+        <v>-0.2132</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5999</v>
+        <v>-0.6208</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4419</v>
+        <v>-0.444</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5581</v>
+        <v>0.556</v>
       </c>
       <c r="G60" t="n">
         <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5581</v>
+        <v>0.556</v>
       </c>
       <c r="I60" t="n">
         <v>0.5607</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2696</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6482</v>
+        <v>-0.6676</v>
       </c>
       <c r="E61" t="n">
         <v>-0.5614</v>
@@ -3262,7 +3262,7 @@
         <v>-0.295</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6695</v>
+        <v>-0.6886</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6142</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2977</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6718</v>
+        <v>-0.6909</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6199</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3017</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6751</v>
+        <v>-0.6942</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6282</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3886</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7483</v>
+        <v>-0.7663</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8092</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4846</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.829</v>
+        <v>-0.8459</v>
       </c>
       <c r="E66" t="n">
         <v>-1.009</v>
@@ -3492,7 +3492,7 @@
         <v>-0.5032</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8447</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0479</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1088</v>
+        <v>-1.1013</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5325</v>
+        <v>-0.5289</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8693</v>
+        <v>-0.8827</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.1088</v>
+        <v>-1.1013</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.0115</v>
+        <v>-2.004</v>
       </c>
       <c r="G68" t="n">
         <v>0.9026999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.0115</v>
+        <v>-2.004</v>
       </c>
       <c r="I68" t="n">
         <v>-2.0209</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5387</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.8908</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1217</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5846</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9131</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2173</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6081</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9329</v>
+        <v>-0.9484</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2662</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.269</v>
+        <v>-1.267</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.6085</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9487</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.269</v>
+        <v>-1.267</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.5498</v>
+        <v>-0.5478</v>
       </c>
       <c r="G72" t="n">
         <v>-0.7192</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.5498</v>
+        <v>-0.5478</v>
       </c>
       <c r="I72" t="n">
         <v>-0.5524</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6103</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9348</v>
+        <v>-0.9502</v>
       </c>
       <c r="E73" t="n">
         <v>-1.2709</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6536999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.9863</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3613</v>
@@ -3860,7 +3860,7 @@
         <v>-0.6629</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.979</v>
+        <v>-0.9938</v>
       </c>
       <c r="E75" t="n">
         <v>-1.3803</v>
@@ -3906,7 +3906,7 @@
         <v>-0.7098</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0185</v>
+        <v>-1.0328</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4781</v>
@@ -3952,7 +3952,7 @@
         <v>-0.762</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0624</v>
+        <v>-1.0761</v>
       </c>
       <c r="E77" t="n">
         <v>-1.5867</v>
@@ -3998,7 +3998,7 @@
         <v>-0.8025</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0964</v>
+        <v>-1.1097</v>
       </c>
       <c r="E78" t="n">
         <v>-1.6711</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8027</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0966</v>
+        <v>-1.1098</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6714</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8174</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.109</v>
+        <v>-1.122</v>
       </c>
       <c r="E80" t="n">
         <v>-1.7021</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.312</v>
+        <v>-2.3064</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.1103</v>
+        <v>-1.1076</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3554</v>
+        <v>-1.3628</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.312</v>
+        <v>-2.3064</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.5083</v>
+        <v>-1.5027</v>
       </c>
       <c r="G81" t="n">
         <v>-0.8037</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.5083</v>
+        <v>-1.5027</v>
       </c>
       <c r="I81" t="n">
         <v>-1.5153</v>
@@ -4182,7 +4182,7 @@
         <v>-1.3345</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.544</v>
+        <v>-1.551</v>
       </c>
       <c r="E82" t="n">
         <v>-2.7789</v>
